--- a/design/蛋仔--大富翁--道具表.xlsx
+++ b/design/蛋仔--大富翁--道具表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\eggitor\1_开发中\大富翁\设计文档\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/billyq/Dev/Github/Lua/monopoly/design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C09473-092B-40C1-90E4-61FF2F763B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4117F55-4CD4-AE49-A3CC-7C696B9FFB41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -246,10 +246,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>使用路障卡，在你前后3格内放置一个路障，任何玩家经过此地时强制停留在此1个回合。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>使用怪兽卡，你可以选择前后3格内的其他玩家建筑，释放怪兽拆除该建筑。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -387,6 +383,10 @@
   </si>
   <si>
     <t>使用请神卡，选择一个其他玩家，将附身于他的神仙请到自己身上。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用路障卡，在你前后3格内放置一个路障，任何玩家经过此地时强制停留。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -394,7 +394,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -743,15 +743,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="5" width="11.875" customWidth="1"/>
+    <col min="4" max="5" width="11.83203125" customWidth="1"/>
     <col min="8" max="8" width="18.5" customWidth="1"/>
-    <col min="9" max="9" width="39.125" customWidth="1"/>
+    <col min="9" max="9" width="39.1640625" customWidth="1"/>
     <col min="10" max="10" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -762,16 +762,16 @@
         <v>28</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>17</v>
@@ -786,7 +786,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -806,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>4</v>
@@ -821,7 +821,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11">
       <c r="A3" s="2">
         <v>2001</v>
       </c>
@@ -832,7 +832,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E3" s="1">
         <v>1</v>
@@ -854,7 +854,7 @@
       </c>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11">
       <c r="A4" s="2">
         <v>2002</v>
       </c>
@@ -865,7 +865,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E4" s="1">
         <v>1000</v>
@@ -887,7 +887,7 @@
       </c>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11">
       <c r="A5" s="2">
         <v>2003</v>
       </c>
@@ -898,7 +898,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E5" s="1">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11">
       <c r="A6" s="2">
         <v>2004</v>
       </c>
@@ -931,7 +931,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E6" s="1">
         <v>1000</v>
@@ -949,11 +949,11 @@
         <v>32</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11">
       <c r="A7" s="2">
         <v>2005</v>
       </c>
@@ -964,7 +964,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E7" s="1">
         <v>1000</v>
@@ -988,7 +988,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11">
       <c r="A8" s="2">
         <v>2006</v>
       </c>
@@ -999,7 +999,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E8" s="1">
         <v>1000</v>
@@ -1020,10 +1020,10 @@
         <v>47</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="2">
         <v>2007</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9" s="1">
         <v>10</v>
@@ -1052,11 +1052,11 @@
         <v>36</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11">
       <c r="A10" s="2">
         <v>2008</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E10" s="1">
         <v>10</v>
@@ -1085,11 +1085,11 @@
         <v>38</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K10" s="1"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11">
       <c r="A11" s="2">
         <v>2009</v>
       </c>
@@ -1100,7 +1100,7 @@
         <v>2</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E11" s="1">
         <v>10</v>
@@ -1124,7 +1124,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11">
       <c r="A12" s="2">
         <v>2010</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>2</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E12" s="1">
         <v>10</v>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11">
       <c r="A13" s="2">
         <v>2011</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E13" s="1">
         <v>10</v>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11">
       <c r="A14" s="2">
         <v>2012</v>
       </c>
@@ -1201,7 +1201,7 @@
         <v>2</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E14" s="1">
         <v>10</v>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11">
       <c r="A15" s="2">
         <v>2013</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E15" s="1">
         <v>5</v>
@@ -1249,27 +1249,27 @@
         <v>22</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>52</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="2">
         <v>2014</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C16" s="1">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E16" s="1">
         <v>5</v>
@@ -1284,27 +1284,27 @@
         <v>22</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J16" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="2">
         <v>2015</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C17" s="1">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E17" s="1">
         <v>5</v>
@@ -1319,25 +1319,25 @@
         <v>22</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11">
       <c r="A18" s="2">
         <v>2016</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C18" s="1">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E18" s="1">
         <v>5</v>
@@ -1349,30 +1349,30 @@
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="K18" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="2">
         <v>2017</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C19" s="1">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E19" s="1">
         <v>5</v>
@@ -1387,25 +1387,25 @@
         <v>22</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11">
       <c r="A20" s="2">
         <v>2018</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C20" s="1">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E20" s="1">
         <v>5</v>
@@ -1420,25 +1420,25 @@
         <v>22</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11">
       <c r="A21" s="2">
         <v>2019</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C21" s="1">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E21" s="1">
         <v>5</v>
@@ -1453,13 +1453,13 @@
         <v>22</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/design/蛋仔--大富翁--道具表.xlsx
+++ b/design/蛋仔--大富翁--道具表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/billyq/Dev/Github/Lua/monopoly/design/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\eggitor\1_开发中\大富翁\monopoly\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4117F55-4CD4-AE49-A3CC-7C696B9FFB41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C69B0A4-2038-4637-BDDF-07C96AF2B67C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-930" yWindow="2055" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="88">
   <si>
     <t>道具id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -311,10 +311,6 @@
   </si>
   <si>
     <t>乐园币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>广告</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -394,7 +390,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -743,15 +739,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="5" width="11.83203125" customWidth="1"/>
+    <col min="4" max="5" width="11.875" customWidth="1"/>
     <col min="8" max="8" width="18.5" customWidth="1"/>
-    <col min="9" max="9" width="39.1640625" customWidth="1"/>
+    <col min="9" max="9" width="39.125" customWidth="1"/>
     <col min="10" max="10" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -771,7 +767,7 @@
         <v>13</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>17</v>
@@ -786,7 +782,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -806,7 +802,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>4</v>
@@ -821,7 +817,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>2001</v>
       </c>
@@ -832,13 +828,13 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E3" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="F3" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G3" s="1" t="b">
         <v>0</v>
@@ -854,7 +850,7 @@
       </c>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2002</v>
       </c>
@@ -868,7 +864,7 @@
         <v>67</v>
       </c>
       <c r="E4" s="1">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="F4" s="1">
         <v>1000</v>
@@ -887,7 +883,7 @@
       </c>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>2003</v>
       </c>
@@ -901,7 +897,7 @@
         <v>67</v>
       </c>
       <c r="E5" s="1">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="F5" s="1">
         <v>1000</v>
@@ -920,7 +916,7 @@
       </c>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>2004</v>
       </c>
@@ -934,7 +930,7 @@
         <v>67</v>
       </c>
       <c r="E6" s="1">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="F6" s="1">
         <v>1000</v>
@@ -949,11 +945,11 @@
         <v>32</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>2005</v>
       </c>
@@ -967,7 +963,7 @@
         <v>67</v>
       </c>
       <c r="E7" s="1">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="F7" s="1">
         <v>1000</v>
@@ -988,7 +984,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>2006</v>
       </c>
@@ -1002,7 +998,7 @@
         <v>67</v>
       </c>
       <c r="E8" s="1">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="F8" s="1">
         <v>1000</v>
@@ -1020,10 +1016,10 @@
         <v>47</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>2007</v>
       </c>
@@ -1037,7 +1033,7 @@
         <v>69</v>
       </c>
       <c r="E9" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F9" s="1">
         <v>500</v>
@@ -1052,11 +1048,11 @@
         <v>36</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>2008</v>
       </c>
@@ -1070,7 +1066,7 @@
         <v>69</v>
       </c>
       <c r="E10" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F10" s="1">
         <v>500</v>
@@ -1089,7 +1085,7 @@
       </c>
       <c r="K10" s="1"/>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>2009</v>
       </c>
@@ -1100,10 +1096,10 @@
         <v>2</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E11" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F11" s="1">
         <v>500</v>
@@ -1124,7 +1120,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>2010</v>
       </c>
@@ -1135,13 +1131,13 @@
         <v>2</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E12" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F12" s="1">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G12" s="1" t="b">
         <v>0</v>
@@ -1157,7 +1153,7 @@
       </c>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>2011</v>
       </c>
@@ -1168,13 +1164,13 @@
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E13" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F13" s="1">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="G13" s="1" t="b">
         <v>1</v>
@@ -1190,7 +1186,7 @@
       </c>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>2012</v>
       </c>
@@ -1201,13 +1197,13 @@
         <v>2</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E14" s="1">
-        <v>10</v>
+        <v>5000</v>
       </c>
       <c r="F14" s="1">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="G14" s="1" t="b">
         <v>1</v>
@@ -1223,7 +1219,7 @@
       </c>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>2013</v>
       </c>
@@ -1240,7 +1236,7 @@
         <v>5</v>
       </c>
       <c r="F15" s="1">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="G15" s="1" t="b">
         <v>0</v>
@@ -1258,12 +1254,12 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>2014</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C16" s="1">
         <v>3</v>
@@ -1272,10 +1268,10 @@
         <v>68</v>
       </c>
       <c r="E16" s="1">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F16" s="1">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G16" s="1" t="b">
         <v>1</v>
@@ -1284,21 +1280,21 @@
         <v>22</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J16" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>2015</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C17" s="1">
         <v>3</v>
@@ -1307,7 +1303,7 @@
         <v>68</v>
       </c>
       <c r="E17" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F17" s="1">
         <v>200</v>
@@ -1319,19 +1315,19 @@
         <v>22</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>2016</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C18" s="1">
         <v>3</v>
@@ -1340,7 +1336,7 @@
         <v>68</v>
       </c>
       <c r="E18" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F18" s="1">
         <v>200</v>
@@ -1349,19 +1345,19 @@
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="K18" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>2017</v>
       </c>
@@ -1375,10 +1371,10 @@
         <v>68</v>
       </c>
       <c r="E19" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F19" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G19" s="1" t="b">
         <v>0</v>
@@ -1394,7 +1390,7 @@
       </c>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>2018</v>
       </c>
@@ -1408,10 +1404,10 @@
         <v>68</v>
       </c>
       <c r="E20" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F20" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G20" s="1" t="b">
         <v>0</v>
@@ -1427,7 +1423,7 @@
       </c>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>2019</v>
       </c>
@@ -1441,10 +1437,10 @@
         <v>68</v>
       </c>
       <c r="E21" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F21" s="1">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G21" s="1" t="b">
         <v>0</v>
@@ -1456,7 +1452,7 @@
         <v>64</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>61</v>
